--- a/Altium/NewPowerElec/GeecPE/Project Outputs for GeecPE/BOM/Bill of Materials-GeecPE(Assembly Variant).xlsx
+++ b/Altium/NewPowerElec/GeecPE/Project Outputs for GeecPE/BOM/Bill of Materials-GeecPE(Assembly Variant).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\Masters\Project\Altium\NewPowerElec\GeecPE\Project Outputs for GeecPE\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BEC2FB1F-EBF5-49AE-A9D3-2E92C4A291E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F9BD7714-4C0B-4190-B636-2D6124CAC716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3600" yWindow="1005" windowWidth="15420" windowHeight="11385" xr2:uid="{A9B27D6C-7A20-4EB0-9B48-E277BABF5E27}"/>
+    <workbookView xWindow="1200" yWindow="1725" windowWidth="16200" windowHeight="15600" xr2:uid="{8C49BD7D-6CB9-4A26-8B66-7F03B96EA801}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-GeecPE(Assemb" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="239">
   <si>
     <t>Comment</t>
   </si>
@@ -65,6 +65,39 @@
     <t>JLCPN</t>
   </si>
   <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Cable Wrap, 1/2 Inch, Polyethylene, Natural, 50 Ft, Spirap Series</t>
+  </si>
+  <si>
+    <t>+3V3, +11V, 5V ISO, MOT, P IN1, P IN2, VBAT</t>
+  </si>
+  <si>
+    <t>FP-5000-MFG</t>
+  </si>
+  <si>
+    <t>CMP-00030-00004-2</t>
+  </si>
+  <si>
+    <t>Not Fitted, Fitted</t>
+  </si>
+  <si>
+    <t>5001</t>
+  </si>
+  <si>
+    <t>Test Point, Mini, Thm, Pc, .300 L, .100 Od, Heat Resistant Nylon 46, Black</t>
+  </si>
+  <si>
+    <t>AGND1, AGND2, AGND3, GND ISO</t>
+  </si>
+  <si>
+    <t>FP-5001-MFG</t>
+  </si>
+  <si>
+    <t>CMP-00030-00001-2</t>
+  </si>
+  <si>
     <t>GCM32EC71H106KA03L</t>
   </si>
   <si>
@@ -254,6 +287,21 @@
     <t>C84256</t>
   </si>
   <si>
+    <t>5002</t>
+  </si>
+  <si>
+    <t>Test Point, Mini, Thm, Pc, .300 L, .100 Od, Heat Resistant Nylon 46, White</t>
+  </si>
+  <si>
+    <t>EN, FAULT, I_Sense, PWM, SCL, SDA, SOFT</t>
+  </si>
+  <si>
+    <t>FP-5002-MFG</t>
+  </si>
+  <si>
+    <t>CMP-00030-00002-2</t>
+  </si>
+  <si>
     <t>691309310012</t>
   </si>
   <si>
@@ -302,19 +350,34 @@
     <t>C2042812</t>
   </si>
   <si>
-    <t>M3 Hole</t>
-  </si>
-  <si>
-    <t>Hole for M3 bolt</t>
-  </si>
-  <si>
-    <t>MH1, MH2, MH3, MH4</t>
-  </si>
-  <si>
-    <t>M3 Hole-Footprint-1</t>
-  </si>
-  <si>
-    <t>CMP-00028-00007-2</t>
+    <t>SEM LOGO</t>
+  </si>
+  <si>
+    <t>SEM Logo Required for Power Electronics</t>
+  </si>
+  <si>
+    <t>LG1</t>
+  </si>
+  <si>
+    <t>SEM LOGO-Footprint-1</t>
+  </si>
+  <si>
+    <t>CMP-00028-00008-2</t>
+  </si>
+  <si>
+    <t>Geec Logo</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>LG2, LG2.</t>
+  </si>
+  <si>
+    <t>Geec Logo-Footprint-1</t>
+  </si>
+  <si>
+    <t>CMP-00028-00009-2</t>
   </si>
   <si>
     <t>7461001</t>
@@ -329,7 +392,7 @@
     <t>7461001_chemical surface</t>
   </si>
   <si>
-    <t>CMP-002-00075-1</t>
+    <t>CMP-002-00075-3</t>
   </si>
   <si>
     <t>61300211121</t>
@@ -344,6 +407,18 @@
     <t>CMP-002-00208-1</t>
   </si>
   <si>
+    <t>61300311121</t>
+  </si>
+  <si>
+    <t>WR-PHD Pin Header, THT, Vertical, pitch 2.54mm, 1 Row, 3P</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>CMP-002-00212-1</t>
+  </si>
+  <si>
     <t>PSMN1R0-30YLDX</t>
   </si>
   <si>
@@ -417,9 +492,6 @@
   </si>
   <si>
     <t>CMP-009-00183-1</t>
-  </si>
-  <si>
-    <t>Not Fitted, Fitted</t>
   </si>
   <si>
     <t>C17888</t>
@@ -1079,8 +1151,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{845F981D-30AF-4184-BE27-ECB948C33A80}">
-  <dimension ref="A1:H39"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A607680-C31C-47E1-9012-796E0AEF8DC2}">
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
@@ -1130,58 +1202,58 @@
         <v>12</v>
       </c>
       <c r="F2" s="1">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1">
-        <v>8</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -1202,36 +1274,34 @@
         <v>28</v>
       </c>
       <c r="F5" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -1252,7 +1322,7 @@
         <v>39</v>
       </c>
       <c r="F7" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>6</v>
@@ -1283,51 +1353,49 @@
       <c r="G8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>46</v>
-      </c>
+      <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="1">
+        <v>8</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="F10" s="1">
         <v>2</v>
@@ -1336,24 +1404,24 @@
         <v>6</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="F11" s="1">
         <v>2</v>
@@ -1362,24 +1430,24 @@
         <v>6</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="F12" s="1">
         <v>2</v>
@@ -1388,84 +1456,84 @@
         <v>6</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>74</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>86</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
@@ -1478,42 +1546,44 @@
         <v>89</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
@@ -1526,61 +1596,63 @@
         <v>99</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H18" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>6</v>
@@ -1589,119 +1661,115 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F21" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H21" s="1"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F22" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>127</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="F24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="F25" s="1">
         <v>1</v>
@@ -1713,45 +1781,43 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F26" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>144</v>
-      </c>
+      <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="F27" s="1">
         <v>4</v>
@@ -1763,69 +1829,71 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="F28" s="1">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H29" s="1"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="F30" s="1">
         <v>1</v>
@@ -1833,75 +1901,73 @@
       <c r="G30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>165</v>
-      </c>
+      <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="E31" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="F31" s="1">
+        <v>8</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" s="1"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="F32" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>176</v>
-      </c>
+      <c r="H32" s="1"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -1909,49 +1975,49 @@
       <c r="G33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="H33" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="F34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H34" s="2" t="s">
-        <v>187</v>
-      </c>
+      <c r="H34" s="1"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="F35" s="1">
         <v>1</v>
@@ -1960,50 +2026,48 @@
         <v>6</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>199</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H36" s="1"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F37" s="1">
         <v>1</v>
@@ -2011,26 +2075,28 @@
       <c r="G37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H37" s="1"/>
+      <c r="H37" s="2" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F38" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>6</v>
@@ -2039,19 +2105,19 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
@@ -2059,7 +2125,133 @@
       <c r="G39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H39" s="1"/>
+      <c r="H39" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H44" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
